--- a/assets/tools_template.xlsx
+++ b/assets/tools_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12210"/>
+    <workbookView windowWidth="24930" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="定检工具" sheetId="1" r:id="rId1"/>
@@ -476,7 +476,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -592,36 +592,6 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -741,7 +711,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -771,7 +741,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -789,28 +759,28 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -819,10 +789,10 @@
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -880,7 +850,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -922,15 +892,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1490,23 +1451,23 @@
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:7">
       <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" customHeight="1" spans="1:7">
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" customHeight="1" spans="1:7">
       <c r="A20" s="9"/>
@@ -1582,23 +1543,23 @@
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:7">
       <c r="A28" s="13"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" customHeight="1" spans="1:7">
       <c r="A29" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" customHeight="1" spans="1:7">
       <c r="A30" s="9"/>
@@ -1674,23 +1635,23 @@
     </row>
     <row r="38" ht="14.25" customHeight="1" spans="1:7">
       <c r="A38" s="13"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="16"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="11"/>
     </row>
     <row r="39" customHeight="1" spans="1:7">
       <c r="A39" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="11"/>
     </row>
     <row r="40" customHeight="1" spans="1:7">
       <c r="A40" s="9"/>
@@ -1766,12 +1727,12 @@
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:7">
       <c r="A48" s="13"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="16"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="5">
